--- a/Config/Datas/Tables/z_表现层级_CombatRenderConfig.xlsx
+++ b/Config/Datas/Tables/z_表现层级_CombatRenderConfig.xlsx
@@ -2346,7 +2346,7 @@
         <x:v>20016</x:v>
       </x:c>
       <x:c r="F120" s="3" t="n">
-        <x:v>30029</x:v>
+        <x:v>30051</x:v>
       </x:c>
       <x:c r="G120" s="3" t="n">
         <x:v>3010</x:v>
@@ -2365,7 +2365,7 @@
         <x:v>20016</x:v>
       </x:c>
       <x:c r="F121" s="3" t="n">
-        <x:v>30030</x:v>
+        <x:v>30052</x:v>
       </x:c>
       <x:c r="G121" s="3" t="n">
         <x:v>3015</x:v>
@@ -2441,7 +2441,7 @@
         <x:v>20030</x:v>
       </x:c>
       <x:c r="F125" s="3" t="n">
-        <x:v>30047</x:v>
+        <x:v>30077</x:v>
       </x:c>
       <x:c r="G125" s="3" t="n">
         <x:v>3010</x:v>
@@ -2460,7 +2460,7 @@
         <x:v>20030</x:v>
       </x:c>
       <x:c r="F126" s="3" t="n">
-        <x:v>30048</x:v>
+        <x:v>30078</x:v>
       </x:c>
       <x:c r="G126" s="3" t="n">
         <x:v>3015</x:v>
@@ -2529,14 +2529,14 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="C130" s="3" t="str">
-        <x:v>不灭罡域 / 护体阵纹</x:v>
+        <x:v>不灭罡域 / 双环表现</x:v>
       </x:c>
       <x:c r="D130" s="3"/>
       <x:c r="E130" s="3" t="n">
         <x:v>20037</x:v>
       </x:c>
       <x:c r="F130" s="3" t="n">
-        <x:v>30065</x:v>
+        <x:v>30097</x:v>
       </x:c>
       <x:c r="G130" s="3" t="n">
         <x:v>3001</x:v>
@@ -2548,56 +2548,36 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="C131" s="3" t="str">
-        <x:v>护体罡环 / 落剑冲击</x:v>
+        <x:v>护体罡环 / 旋转护环</x:v>
       </x:c>
       <x:c r="D131" s="3"/>
       <x:c r="E131" s="3" t="n">
         <x:v>20043</x:v>
       </x:c>
       <x:c r="F131" s="3" t="n">
-        <x:v>30063</x:v>
+        <x:v>30097</x:v>
       </x:c>
       <x:c r="G131" s="3" t="n">
-        <x:v>3015</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="28" customHeight="1">
       <x:c r="A132" s="3"/>
-      <x:c r="B132" s="3" t="n">
-        <x:v>1018</x:v>
-      </x:c>
-      <x:c r="C132" s="3" t="str">
-        <x:v>护体罡环 / 后景光柱</x:v>
-      </x:c>
+      <x:c r="B132" s="3"/>
+      <x:c r="C132" s="3"/>
       <x:c r="D132" s="3"/>
-      <x:c r="E132" s="3" t="n">
-        <x:v>20043</x:v>
-      </x:c>
-      <x:c r="F132" s="3" t="n">
-        <x:v>30064</x:v>
-      </x:c>
-      <x:c r="G132" s="3">
-        <x:v>3002</x:v>
-      </x:c>
+      <x:c r="E132" s="3"/>
+      <x:c r="F132" s="3"/>
+      <x:c r="G132" s="3"/>
     </x:row>
     <x:row r="133" ht="28" customHeight="1">
       <x:c r="A133" s="3"/>
-      <x:c r="B133" s="3" t="n">
-        <x:v>1019</x:v>
-      </x:c>
-      <x:c r="C133" s="3" t="str">
-        <x:v>护体罡环 / 地面阵纹</x:v>
-      </x:c>
+      <x:c r="B133" s="3"/>
+      <x:c r="C133" s="3"/>
       <x:c r="D133" s="3"/>
-      <x:c r="E133" s="3" t="n">
-        <x:v>20043</x:v>
-      </x:c>
-      <x:c r="F133" s="3" t="n">
-        <x:v>30065</x:v>
-      </x:c>
-      <x:c r="G133" s="3" t="n">
-        <x:v>3000</x:v>
-      </x:c>
+      <x:c r="E133" s="3"/>
+      <x:c r="F133" s="3"/>
+      <x:c r="G133" s="3"/>
     </x:row>
     <x:row r="134" ht="28" customHeight="1">
       <x:c r="A134" s="3"/>
@@ -2656,6 +2636,108 @@
         <x:v>3015</x:v>
       </x:c>
     </x:row>
+    <x:row r="137">
+      <x:c r="B137" s="3" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="C137" s="3" t="str">
+        <x:v>追星飞刃 / 随身施法</x:v>
+      </x:c>
+      <x:c r="E137" s="3" t="n">
+        <x:v>20001</x:v>
+      </x:c>
+      <x:c r="F137" s="3" t="n">
+        <x:v>30004</x:v>
+      </x:c>
+      <x:c r="G137" s="3" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="B138" s="3" t="n">
+        <x:v>1102</x:v>
+      </x:c>
+      <x:c r="C138" s="3" t="str">
+        <x:v>连锁灵梭 / 随身施法</x:v>
+      </x:c>
+      <x:c r="E138" s="3" t="n">
+        <x:v>20016</x:v>
+      </x:c>
+      <x:c r="F138" s="3" t="n">
+        <x:v>30053</x:v>
+      </x:c>
+      <x:c r="G138" s="3" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="B139" s="3" t="n">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="C139" s="3" t="str">
+        <x:v>焚天龙符 / 随身施法</x:v>
+      </x:c>
+      <x:c r="E139" s="3" t="n">
+        <x:v>20027</x:v>
+      </x:c>
+      <x:c r="F139" s="3" t="n">
+        <x:v>30044</x:v>
+      </x:c>
+      <x:c r="G139" s="3" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="B140" s="3" t="n">
+        <x:v>1104</x:v>
+      </x:c>
+      <x:c r="C140" s="3" t="str">
+        <x:v>御龙连梭 / 随身施法</x:v>
+      </x:c>
+      <x:c r="E140" s="3" t="n">
+        <x:v>20030</x:v>
+      </x:c>
+      <x:c r="F140" s="3" t="n">
+        <x:v>30079</x:v>
+      </x:c>
+      <x:c r="G140" s="3" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="B141" s="3" t="n">
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="C141" s="3" t="str">
+        <x:v>skill_32 / 随身施法</x:v>
+      </x:c>
+      <x:c r="E141" s="3" t="n">
+        <x:v>20032</x:v>
+      </x:c>
+      <x:c r="F141" s="3" t="n">
+        <x:v>30053</x:v>
+      </x:c>
+      <x:c r="G141" s="3" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="B142" s="3" t="n">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="C142" s="3" t="str">
+        <x:v>万象星羽 / 随身施法</x:v>
+      </x:c>
+      <x:c r="E142" s="3" t="n">
+        <x:v>20044</x:v>
+      </x:c>
+      <x:c r="F142" s="3" t="n">
+        <x:v>30069</x:v>
+      </x:c>
+      <x:c r="G142" s="3" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
